--- a/analysis/tables/bloom-3b.xlsx
+++ b/analysis/tables/bloom-3b.xlsx
@@ -536,27 +536,27 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.9404384522013414</v>
+        <v>0.7586203514424157</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.2347244353821984</v>
+        <v>-0.1908373076128029</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>y = 0.940x - 0.235</t>
+          <t>y = 0.759x - 0.191</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.782231996944451</v>
+        <v>0.7822319969444516</v>
       </c>
       <c r="H3" t="n">
         <v>0.07862700020472366</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2495904275636164</v>
+        <v>0.2515583812772108</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7057140168191429</v>
+        <v>0.5677830438296128</v>
       </c>
       <c r="K3" t="n">
         <v>0.14093043707678</v>
@@ -577,27 +577,27 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.9096146551074421</v>
+        <v>0.7523284357116227</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.1378048728044031</v>
+        <v>-0.1810058007552863</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>y = 0.910x - 0.138</t>
+          <t>y = 0.752x - 0.181</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.806745011545474</v>
+        <v>0.7857354348774375</v>
       </c>
       <c r="H4" t="n">
-        <v>0.07763520775569017</v>
+        <v>0.07848525169503817</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1514980789179632</v>
+        <v>0.2405941237407491</v>
       </c>
       <c r="J4" t="n">
-        <v>0.771809782303039</v>
+        <v>0.5713226349563363</v>
       </c>
       <c r="K4" t="n">
         <v>0.14093043707678</v>
